--- a/artfynd/A 30085-2025 artfynd.xlsx
+++ b/artfynd/A 30085-2025 artfynd.xlsx
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17081112</v>
+        <v>17081116</v>
       </c>
       <c r="B2" t="n">
-        <v>85150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3567</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blyspindling agg.</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocinctus s. lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525537.8464157837</v>
+        <v>525489</v>
       </c>
       <c r="R2" t="n">
-        <v>7037803.837472725</v>
+        <v>7037788</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +752,9 @@
           <t>2014-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig kalkgranskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>med guckusko</t>
+          <t>medelålders risfattig granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>

--- a/artfynd/A 30085-2025 artfynd.xlsx
+++ b/artfynd/A 30085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,8 +792,16 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17081116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>